--- a/DS/data.xlsx
+++ b/DS/data.xlsx
@@ -413,49 +413,5774 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Age</t>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>EAN</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Internal ID</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Alice</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Compact Printer Air Advanced Digital</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Situation organization these memory much off.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Garner, Boyle and Flynn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Books &amp; Stationery</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>265</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>774</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2091465262179</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ForestGreen</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Discussion loss politics free one thousand.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mueller Inc</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Shoes &amp; Footwear</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>502</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>81</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5286196620740</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>8x10 in</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Smart Blender Cooker</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>No situation per.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Lawson, Keller and Winters</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Kitchen Appliances</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>227</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>726</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1282898648918</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>SlateGray</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Advanced Router Rechargeable</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>For force gas energy six laugh.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Gallagher and Sons</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Kitchen Appliances</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>121</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>896</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3879177514583</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PaleGreen</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>discontinued</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Portable Mouse Monitor Phone</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Feeling back religious however author room scientist.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Irwin LLC</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Kids' Clothing</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>925</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9055773261265</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SeaShell</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>100x200 mm</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>discontinued</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Radio</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Character prove growth contain serious customer.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Benjamin, Nelson and Hancock</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>426</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>549</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1150028980156</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>CornflowerBlue</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>30x40 cm</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ultra Projector Oven Thermostat Prime Advanced</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pattern possible look necessary indicate work nearly.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mccoy, Waters and Rose</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Laptops &amp; Computers</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>68</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>870</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5029747624534</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Purple</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>discontinued</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Webcam Stove Grill</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Deep area join carry age.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Morrow and Sons</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>159</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>584</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9883725074294</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>MediumOrchid</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>8x10 in</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Eco Radio</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Know father for act let.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Edwards, Odonnell and Conley</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>454</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>499</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1773215338624</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>DimGray</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ultra Powerbank Brush Charger Max</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Meeting add economic task outside.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Brennan, Archer and Rosales</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Fitness Equipment</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>845</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>564</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4877111475333</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Extra Large</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>discontinued</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Wireless Dock</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Whole bill sound whether will.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Russo-West</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>257</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>168</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9680811891595</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Extra Large</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fast Camera Router Fan Smart</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Various above trouble itself crime form.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Vazquez and Sons</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cleaning Supplies</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>221</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>672</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8567222480604</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>MidnightBlue</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Heater Radio</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ten do evidence billion perhaps read bank enter.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Delgado-Blackwell</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Cycling</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>689</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>156</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5686660235911</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Smart Trimmer Webcam Heater</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Example available better.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Contreras PLC</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>279</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>818</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1941032767914</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Gainsboro</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Webcam Dock Heater</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>State yet soon traditional your deal.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Juarez, Powell and Travis</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Cleaning Supplies</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>101</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>159</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1438856474369</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sienna</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>30x40 cm</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Automatic Watch Lite Sense</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>As east entire positive source their.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Reid, Chase and Ballard</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Team Sports</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>316</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>329</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3500722785805</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Tan</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>5x7 in</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>limited_stock</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Eco Iron Monitor Air</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Color single indeed yard event popular food boy.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Barker-Murphy</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>982</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>47</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7887280730963</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>OliveDrab</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>out_of_stock</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Digital Tablet Router Printer Lite</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Accept campaign every research test.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Vazquez-Smith</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>732</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4170125892616</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>LemonChiffon</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>10x10 cm</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>backorder</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Eco Freezer Powerbank Watch</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Of price visit interesting enter three set.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Pruitt, Higgins and Barnett</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cleaning Supplies</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>340</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>618</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6340907128242</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Cyan</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>limited_stock</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cooler Fan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fall billion city share.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bray LLC</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Smartphones</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>529</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>844</v>
+      </c>
+      <c r="I21" t="n">
+        <v>267078141619</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Bisque</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>backorder</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Portable Camera Plus Air Ultra</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Reality hair explain up bad.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Wang-Valenzuela</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Women's Clothing</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>197</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>163</v>
+      </c>
+      <c r="I22" t="n">
+        <v>963840013930</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Magenta</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Wireless Powerbank 360 Advanced Ultra</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Deal head decade age outside military culture.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Carney Ltd</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Bedding &amp; Bath</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>677</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>418</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3918763032312</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Beige</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>out_of_stock</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rechargeable Lamp Speakerphone Headphones</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Effort own safe main walk quickly.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Gallegos, Osborne and Carpenter</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>664</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>577</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1824359393441</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>DarkBlue</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mini Scooter Microphone</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Maybe around expect own whether pay.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Douglas, Thornton and Soto</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Grooming Tools</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>784</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>510</v>
+      </c>
+      <c r="I25" t="n">
+        <v>9839666739792</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>DimGray</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>backorder</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Bob</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rechargeable Webcam Stove Grill</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Movement you Mr decide history effect.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Horn-Pope</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>900</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>623</v>
+      </c>
+      <c r="I26" t="n">
+        <v>6501687247749</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PaleGreen</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>5x7 in</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>out_of_stock</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Mini Iron Drone Wireless Pro</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>From Congress low.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Khan-Parrish</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Cycling</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>909</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>797</v>
+      </c>
+      <c r="I27" t="n">
+        <v>9496081864722</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>CadetBlue</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>limited_stock</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Portable Freezer Phone Automatic Smart</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Live fish audience piece his ago true.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Burton PLC</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>350</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>756</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3486711401836</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Snow</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Wireless Webcam Stove Grill</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Pull at improve health also animal forward person.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Henry Group</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Clothing &amp; Apparel</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>858</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>912</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7097613907430</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>LightSalmon</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>50x70 cm</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>limited_stock</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Clock Brush</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Other another must explain send somebody consider.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Larson-Spence</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>985</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>180</v>
+      </c>
+      <c r="I30" t="n">
+        <v>8301096575048</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>SaddleBrown</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Extra Large</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
         <v>30</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Charlie</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Keyboard Toaster Monitor</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>My head prove exist change.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Bonilla-Spears</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Kids' Clothing</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>576</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>988</v>
+      </c>
+      <c r="I31" t="n">
+        <v>6639325474032</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>DarkSlateGray</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Silent Printer Fan Shaver</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Region week yet weight.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Love LLC</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sports &amp; Outdoors</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>102</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>669</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5564792899662</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>MediumSpringGreen</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>limited_stock</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Wireless Scooter Clean Mini</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Green main imagine way suffer wall.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Terry-Oliver</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Fragrances</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>283</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>343</v>
+      </c>
+      <c r="I33" t="n">
+        <v>9921752342730</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>MintCream</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Advanced Microphone Cooler Eco</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Most other newspaper beyond real.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Morales, Weaver and Fernandez</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Smartphones</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>904</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>532</v>
+      </c>
+      <c r="I34" t="n">
+        <v>7107438924403</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>LightCyan</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Extra Large</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>limited_stock</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Automatic Brush Fast Eco</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Record response relationship.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Newman Ltd</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Kids' Clothing</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>407</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>285</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2327483415120</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>SeaGreen</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>8x10 in</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>out_of_stock</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
         <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Premium Bicycle Microphone</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Congress how list third rise.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Novak, Archer and Walton</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Shoes &amp; Footwear</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>480</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>364</v>
+      </c>
+      <c r="I36" t="n">
+        <v>6209821998907</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>AliceBlue</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Extra Large</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>discontinued</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Smart Phone Scooter Clean</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Reality kid create thought window.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Marshall-Dougherty</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Women's Clothing</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>635</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>727</v>
+      </c>
+      <c r="I37" t="n">
+        <v>7883295446066</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>MediumVioletRed</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>10x10 cm</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>backorder</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bicycle</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Garden mother before ten different increase.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Hays-Cunningham</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Smartphones</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>234</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>394</v>
+      </c>
+      <c r="I38" t="n">
+        <v>7670612815694</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>10x10 cm</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>backorder</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ultra Dock Trimmer Automatic Edge</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Do customer stage act send.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Barnes-Glass</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Kids' Clothing</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>640</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>780</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2837107354495</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>LightBlue</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>5x7 in</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>discontinued</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Wireless Tablet Router Printer Wireless Premium Air</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>North meeting short summer situation positive candidate.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Meyers-Hess</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Sports &amp; Outdoors</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>781</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>947</v>
+      </c>
+      <c r="I40" t="n">
+        <v>8247903213713</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>BlanchedAlmond</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>out_of_stock</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Clean Printer Advanced Premium Sense</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Bag away always often join seat direction.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Williamson PLC</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Haircare</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>913</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>820</v>
+      </c>
+      <c r="I41" t="n">
+        <v>5234087663802</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Moccasin</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>discontinued</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Silent Dock Fast</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Speak not hospital bit part.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>May, Hendrix and Robbins</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Fishing &amp; Hunting</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>100</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>802</v>
+      </c>
+      <c r="I42" t="n">
+        <v>938364240247</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>CadetBlue</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>limited_stock</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ultra Speakerphone Oven Go Smart X</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Value bill yeah tell phone.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Zimmerman, Barr and Davis</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>999</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>853</v>
+      </c>
+      <c r="I43" t="n">
+        <v>450118214736</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>MediumOrchid</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>12x18 in</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Rechargeable Projector Pro</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Bank everything ago girl.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Levine, Martin and Mccann</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Home Decor</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>935</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>55</v>
+      </c>
+      <c r="I44" t="n">
+        <v>655296358115</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>SlateBlue</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>limited_stock</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Eco Vacuum</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Bit name seat sea.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Werner PLC</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>259</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>668</v>
+      </c>
+      <c r="I45" t="n">
+        <v>8611986118980</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>LightCoral</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5x7 in</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Smart Grill Tablet Fridge Go Smart Smart</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>By result ago born become.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Huff, Cameron and Stephenson</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Fitness Equipment</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>488</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>966</v>
+      </c>
+      <c r="I46" t="n">
+        <v>9005775281402</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Cornsilk</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>10x10 cm</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>out_of_stock</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Digital Stove Silent Pro</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Suffer range between step mention peace prepare.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Suarez, Riddle and Sanders</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>161</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>349</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5367012957872</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>OrangeRed</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Extra Large</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>limited_stock</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Portable Powerbank X Air</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Present court note medical bed red movie.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Hanson-Schultz</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Camping &amp; Hiking</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>599</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>263</v>
+      </c>
+      <c r="I48" t="n">
+        <v>6854117854742</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Moccasin</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>discontinued</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Clock</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Onto story what job require.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Malone, Jacobson and Hudson</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Team Sports</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>731</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>664</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1382809012286</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>FloralWhite</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>limited_stock</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Radio Treadmill</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Through choose record prove happen.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Barron-Little</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>511</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>395</v>
+      </c>
+      <c r="I50" t="n">
+        <v>5461960384619</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Violet</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>discontinued</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Ultra Cooler Treadmill Touch Pro Ultra</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Certainly simple light safe child PM candidate.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bonilla-Oconnell</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Fragrances</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>214</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>574</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3625664059934</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>NavajoWhite</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Mini Fridge Camera</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Little determine at huge month.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Decker and Sons</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Fitness Equipment</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>777</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>832</v>
+      </c>
+      <c r="I52" t="n">
+        <v>4894233116968</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>PaleGoldenRod</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Extra Large</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Rechargeable Tablet Plus Portable Mini</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Expect question how sound.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Mooney-Gonzales</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Fragrances</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>820</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>535</v>
+      </c>
+      <c r="I53" t="n">
+        <v>8183922928019</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Cyan</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>100x200 mm</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Many deal community public beyond safe anyone.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Blake, Weiss and Montgomery</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>408</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>922</v>
+      </c>
+      <c r="I54" t="n">
+        <v>8183313115592</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Chocolate</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>backorder</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Wireless Light Toaster Lite Touch Eco</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Oil guy table industry hand which.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Singleton PLC</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Bedding &amp; Bath</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>791</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>827</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3057639268476</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Fuchsia</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>50x70 cm</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Scooter</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Small approach possible choose according.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Rivas Group</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Cameras &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>370</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>601</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1974896712011</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>DarkOrchid</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>backorder</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Advanced Camera Heater Webcam X Ultra Prime</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Audience bit past central film each.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Cervantes Ltd</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>224</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>372</v>
+      </c>
+      <c r="I57" t="n">
+        <v>983367163970</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>50x70 cm</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>discontinued</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Ultra Keyboard Compact Eco</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Bit responsibility cover him mean call civil.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pace-Hodges</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Books &amp; Stationery</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>514</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>491</v>
+      </c>
+      <c r="I58" t="n">
+        <v>8481605893389</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>LightGray</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>8x10 in</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>backorder</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Portable Scale Speaker Powerbank Clean</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Throughout special new you view season within.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Morris LLC</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Women's Clothing</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>689</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>332</v>
+      </c>
+      <c r="I59" t="n">
+        <v>5175038823985</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>PowderBlue</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>backorder</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Oven Speaker Fan</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Hot behavior traditional.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Schwartz Ltd</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Men's Clothing</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>489</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>423</v>
+      </c>
+      <c r="I60" t="n">
+        <v>2567562782853</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>GoldenRod</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Automatic Speaker Router Lamp Prime</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Word score education thousand high treatment.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Sexton, Dickerson and Blair</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Grooming Tools</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>621</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>667</v>
+      </c>
+      <c r="I61" t="n">
+        <v>6744198567221</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>FireBrick</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>5x7 in</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Smart Webcam Projector Lock</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Subject agree you off.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Stokes Inc</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Men's Clothing</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>440</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>973</v>
+      </c>
+      <c r="I62" t="n">
+        <v>4811928042234</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>SteelBlue</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Fast Fan</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Avoid very final food scene possible.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Ali-Oliver</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Cleaning Supplies</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>982</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>804</v>
+      </c>
+      <c r="I63" t="n">
+        <v>3388615003133</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>DarkOrchid</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>100x200 mm</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>backorder</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Automatic Cooler Edge</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Career for much exist.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Odonnell, Boyle and Oconnor</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>124</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>513</v>
+      </c>
+      <c r="I64" t="n">
+        <v>6261793125392</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>LimeGreen</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>50x70 cm</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Advanced Freezer Advanced Advanced</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Chance material himself soldier.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Gill LLC</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>489</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>561</v>
+      </c>
+      <c r="I65" t="n">
+        <v>6474143371206</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Silent Trimmer Shaver Fast</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Task point seat better.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Munoz Group</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Smartphones</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>130</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>876</v>
+      </c>
+      <c r="I66" t="n">
+        <v>4089415274929</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>DarkSlateGray</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>5x7 in</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Treadmill</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Vote only run modern.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Frost, Christensen and Burnett</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Women's Clothing</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>731</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>744</v>
+      </c>
+      <c r="I67" t="n">
+        <v>4598541150958</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Cyan</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>5x7 in</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>out_of_stock</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Mini Charger Lock Oven Sense Sense</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Major tell him share allow.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Burton, Gross and Giles</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Haircare</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>750</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>623</v>
+      </c>
+      <c r="I68" t="n">
+        <v>9282813513019</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Olive</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>12x18 in</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Thermostat Trimmer</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Drug interview hotel decide pattern.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Hester, Love and Lynch</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Accessories (Bags, Hats, Belts)</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>206</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>677</v>
+      </c>
+      <c r="I69" t="n">
+        <v>8282848236311</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>MidnightBlue</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>8x10 in</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>discontinued</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Clean Iron Premium Air Wireless</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Around tough popular present sign herself pattern.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Shepherd, Greene and House</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>293</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>700</v>
+      </c>
+      <c r="I70" t="n">
+        <v>7935749142557</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>GhostWhite</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>out_of_stock</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Compact Mouse Mouse Router Mini</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Occur miss son Democrat happy.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Barry PLC</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Smartwatches</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>5</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>247</v>
+      </c>
+      <c r="I71" t="n">
+        <v>252926529077</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>PapayaWhip</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>10x10 cm</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>limited_stock</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Premium Lock Mini Advanced</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Three character traditional maybe.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Elliott, Mcfarland and Duran</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>12</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>439</v>
+      </c>
+      <c r="I72" t="n">
+        <v>3997003361528</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Plum</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Silent Webcam Webcam Treadmill Sense Portable Advanced</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Leg my mother father.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>George-Day</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Makeup</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>148</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>650</v>
+      </c>
+      <c r="I73" t="n">
+        <v>6908065460286</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Aqua</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>backorder</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Compact Thermostat Oven</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Focus that consumer amount half.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Hull Inc</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Home &amp; Kitchen</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>685</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>747</v>
+      </c>
+      <c r="I74" t="n">
+        <v>7695934105636</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>SaddleBrown</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>30x40 cm</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Wireless Watch Tablet Printer Automatic Eco Sense</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Might poor animal must protect blue forward.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Fleming Inc</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Smartwatches</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>59</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>169</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1089969929675</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Sienna</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>out_of_stock</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Automatic Blender</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Smile human machine section bank.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Mahoney-Bryan</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Home Decor</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>630</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>438</v>
+      </c>
+      <c r="I76" t="n">
+        <v>310774792552</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>LightGoldenRodYellow</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>8x10 in</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>backorder</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Rechargeable Webcam Dock Heater</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Organization address section collection church gun consumer do.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Kennedy-Gordon</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Cycling</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>800</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>151</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1340784358003</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Clean Toaster Oven Air Touch</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Heavy threat beautiful material assume piece.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Olsen-Sawyer</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Kids' Clothing</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>365</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>71</v>
+      </c>
+      <c r="I78" t="n">
+        <v>7806787405877</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>LimeGreen</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Brush</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Control daughter effect investment piece training nation.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Lowe, Mosley and Rivera</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Bedding &amp; Bath</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>273</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>623</v>
+      </c>
+      <c r="I79" t="n">
+        <v>168419438521</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>RoyalBlue</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Portable Kettle</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Apply out industry must tell.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Sampson-Leon</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Home &amp; Kitchen</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>50</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>413</v>
+      </c>
+      <c r="I80" t="n">
+        <v>445370808496</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>MediumAquaMarine</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Rechargeable Brush Compact</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Early century every amount than past.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Castro-Mccarty</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>748</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>326</v>
+      </c>
+      <c r="I81" t="n">
+        <v>6855062072649</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Sienna</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>out_of_stock</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Fast Heater Cooker Compact Silent</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Strategy fund mind rather change.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Decker, Montes and Logan</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Makeup</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>367</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>19</v>
+      </c>
+      <c r="I82" t="n">
+        <v>3868467036959</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Orchid</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>8x10 in</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Mini Drone X Portable</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Shoulder cost especially.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Whitney Group</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Books &amp; Stationery</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>352</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>123</v>
+      </c>
+      <c r="I83" t="n">
+        <v>9437200314292</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>BlueViolet</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>backorder</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Heater Keyboard</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Remember here kind enjoy source room reflect be.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Brooks and Sons</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>103</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>208</v>
+      </c>
+      <c r="I84" t="n">
+        <v>5328785590239</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Chocolate</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Extra Large</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>backorder</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Wireless Fan Thermostat Max Automatic Max</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Design price for especially section college over green.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Kaiser-Banks</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Books &amp; Stationery</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>423</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>759</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1396411470228</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>MidnightBlue</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>5x7 in</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Fast Keyboard</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Success other institution fear.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Lewis Ltd</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Camping &amp; Hiking</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>998</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>10</v>
+      </c>
+      <c r="I86" t="n">
+        <v>3163238295239</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Cyan</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>50x70 cm</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>limited_stock</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Ultra Mixer Toaster Toaster Smart</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Much guess have pattern southern true hair miss.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Galloway and Sons</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Women's Clothing</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>342</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>221</v>
+      </c>
+      <c r="I87" t="n">
+        <v>4862330962177</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Silent Speakerphone Scanner Monitor</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Quality yet significant lawyer face field yet realize.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Cowan Inc</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Fragrances</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>593</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>580</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1710131812265</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>discontinued</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Silent Scanner Monitor Treadmill</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Do interesting suggest agreement range admit rule.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Nichols, Howe and Miller</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>30</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>728</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1287056757693</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>10x10 cm</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Fast Vacuum Cooler</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Explain six firm recent rock skin.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Blair-Russell</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Sports &amp; Outdoors</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>307</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>320</v>
+      </c>
+      <c r="I90" t="n">
+        <v>4874329354658</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>LightSalmon</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>limited_stock</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Digital Trimmer</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ago floor nice member wait.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Christian-Tanner</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Laptops &amp; Computers</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>541</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>488</v>
+      </c>
+      <c r="I91" t="n">
+        <v>4147810179628</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>SteelBlue</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Automatic Trimmer Sense</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Much table ground information news senior.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Harrington-Valentine</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Kitchen Appliances</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>405</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>950</v>
+      </c>
+      <c r="I92" t="n">
+        <v>524638185</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>SlateGray</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>8x10 in</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Portable Scooter Wireless Digital</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Thousand various evidence.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Bauer Inc</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Cameras &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>519</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>495</v>
+      </c>
+      <c r="I93" t="n">
+        <v>4564280934296</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>DeepSkyBlue</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Fridge Cooker</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Try better loss pretty special.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Jackson Group</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>393</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>499</v>
+      </c>
+      <c r="I94" t="n">
+        <v>1861389468671</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>in_stock</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Scanner</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Draw material quickly most.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Wang, Ayala and Bowen</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Cleaning Supplies</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>472</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>63</v>
+      </c>
+      <c r="I95" t="n">
+        <v>7794860625802</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>ForestGreen</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>12x18 in</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>backorder</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ultra Radio Radio</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Shoulder red boy away if.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Maldonado-Ritter</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Haircare</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>382</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>639</v>
+      </c>
+      <c r="I96" t="n">
+        <v>3611080124547</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Aquamarine</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>12x18 in</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>pre_order</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Router</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Investment everything story buy.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Atkinson Inc</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Laptops &amp; Computers</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>375</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>703</v>
+      </c>
+      <c r="I97" t="n">
+        <v>3330396409604</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Gainsboro</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>8x10 in</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>limited_stock</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Fast Thermostat Microphone Scooter</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Nature notice themselves news.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Shea Ltd</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>289</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>727</v>
+      </c>
+      <c r="I98" t="n">
+        <v>9265397743935</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Extra Large</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>backorder</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Eco Heater Toaster Stove Silent Sense</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Understand still or summer rule.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>West Ltd</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Cleaning Supplies</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>232</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>998</v>
+      </c>
+      <c r="I99" t="n">
+        <v>5505866454530</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>OldLace</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>limited_stock</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Clean Blender Scale Lite</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Final art some push.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Bell, Gamble and Barrett</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Camping &amp; Hiking</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>241</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>391</v>
+      </c>
+      <c r="I100" t="n">
+        <v>3893594435450</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Aquamarine</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>5x7 in</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>limited_stock</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Smart Lamp</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>However public major baby.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Hebert, Hughes and Trujillo</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Bedding &amp; Bath</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>71</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>518</v>
+      </c>
+      <c r="I101" t="n">
+        <v>8264263605712</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>limited_stock</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
